--- a/deliverables/WMP/WMP__Solution_Design_Gap_Register__20260825.xlsx
+++ b/deliverables/WMP/WMP__Solution_Design_Gap_Register__20260825.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Resolved Decisions" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Gap Register'!$A$1:$K$17</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Resolved Decisions'!$A$1:$E$49</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Gap Register'!$A$1:$K$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Resolved Decisions'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="329">
   <si>
     <t xml:space="preserve">WMP Solution Design — Inputs &amp; Decisions Gap Register</t>
   </si>
   <si>
-    <t xml:space="preserve">Rev 6 — 8/25/2026: WMP status dispositions applied; the 16 remaining rows are phrased as short, call-ready questions.</t>
+    <t xml:space="preserve">Rev 7 — 8/25/2026: call answers applied (decommission gate, post-Exchange ownership, operations scope). 13 call-ready rows remain.</t>
   </si>
   <si>
     <t xml:space="preserve">Wisconsin Metal Parts — Microsoft GCC High Migration (CMMC 2.0 Level 2)  |  Prepared by Essendis</t>
@@ -403,58 +403,6 @@
   </si>
   <si>
     <t xml:space="preserve">New section: Endpoint Configuration &gt; On-Premises Resource Access; Device Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The pre-decommission gate lists what must be true but not how it is proven. "No applications or services still authenticating" and "no SMTP relay dependencies" are assertions with no monitoring method, no observation period, and no evidence artifact; the monitored-hold duration is left as "until confirmed idle".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decommission is one-way past the point of hybrid removal; a relay client discovered afterwards means mail loss with only a server backup as the recovery route.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How long is the monitored hold before Exchange removal — 7, 14, or 30 days?
-Who at WMP signs the decommission authorisation?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migration Design &gt; Pre-Decommission Validation Gate; Monitored Hold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The document states that after decommission, recipient management moves to "Entra ID Connect and PowerShell against Active Directory attributes" with no Exchange management server retained — but no runbook, tooling, or skills transfer is defined for that day-2 reality.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creating a mailbox, adding a proxy address, or building a distribution list from raw AD attributes is error-prone and unfamiliar; WMP will need to do it in week one after handoff and there is nothing written to follow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Who at WMP will manage mailboxes/aliases/groups after Exchange is gone? (Essendis provides the PowerShell runbook and training.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migration Design &gt; Hybrid Configuration and Directory Services; As-Configured document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is no monitoring or alerting design. The only alert in the document is break-glass sign-in detection "via Log Analytics in Azure" — a service that is out of scope — and nothing routes Defender, Intune, identity, or service-health alerts to a human.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMMC AU.L2-3.3.1/3.3.5 and IR.L2-3.6.1 expect logs to be reviewed and incidents detected; alerts nobody receives are not a detective control, and the break-glass alert as designed cannot be built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An Azure subscription exists: use Log Analytics for break-glass/audit alerting, or stay M365-native?
-Who receives security alerts (Defender, Intune, Entra) — which mailbox or Teams channel?
-What log-review cadence and owner should we document?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is an available Azure subscription, need to make decision whether log analytics is required.
-WMP (8/25): an Azure subscription is available — decide whether Log Analytics is used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Security &gt; Emergency Accounts; new "Monitoring &amp; Alerting" section</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -908,6 +856,30 @@
     <t xml:space="preserve">Windows device inventory by site/type is collected by WMP during pre-migration device preparation (WBS 7.1.1); Windows 11/TPM exceptions are handled wave-by-wave; servers remain out of scope (G-28).</t>
   </si>
   <si>
+    <t xml:space="preserve">G-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pre-decommission gate lists what must be true but not how it is proven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMP (8/25, via chat): 7-day monitored hold; Kyle Mandersfield signs the decommission authorization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design update: the pre-removal monitored hold is 7 days and the decommission authorization is signed by Kyle Mandersfield (WMP). Essendis defines the residual-connection evidence check within that window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The document states that after decommission, recipient management moves to "Entra ID Connect and PowerShell against Active Directory attributes" with no Exchange management server retained — but no runbook, tooling, or skills transfer is defined for that day-2 reality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMP (8/25, via chat): Essendis is not providing runbooks for PowerShell-based management; WMP owns the processes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design update: post-decommission recipient management is WMP-owned. The design notes management continues via Entra Connect/PowerShell with no Essendis runbook deliverable.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-51</t>
   </si>
   <si>
@@ -918,6 +890,18 @@
   </si>
   <si>
     <t xml:space="preserve">Support model set: hypercare runs one week post-migration with a 2-hour response objective; requests via email and Teams; WMP handles user-facing support thereafter. Essendis documents this in the Communications/support section.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no monitoring or alerting design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMP (8/25, via chat): Operations and support are out of scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope decision: monitoring, alerting, and log-review design are out of engagement scope — WMP decides (an Azure subscription exists if Log Analytics is wanted). Essendis's remaining action is the G-03 cleanup: reword the design's break-glass 'Log Analytics in Azure' reference to reflect WMP-owned alerting.</t>
   </si>
   <si>
     <t xml:space="preserve">G-53</t>
@@ -1264,24 +1248,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1289,7 +1277,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1297,19 +1285,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1326,6 +1314,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1633,187 +1625,187 @@
   <dimension ref="B2:F25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B18)</f>
         <v>2</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!J:J,"High")</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B19)</f>
         <v>2</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!J:J,"Medium")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B20)</f>
         <v>3</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <f aca="false">COUNTA('Gap Register'!A:A)-1</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B21)</f>
         <v>1</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <f aca="false">COUNTA('Resolved Decisions'!A:A)-1</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B22)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B23)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B24)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1840,602 +1832,540 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+    <row r="2" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13" t="s">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="4" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+    <row r="6" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+    <row r="7" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13" t="s">
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+    <row r="8" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+    <row r="12" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
+      <c r="G12" s="14"/>
+      <c r="H12" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+    <row r="14" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>42</v>
-      </c>
+    <row r="15" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K14"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2452,850 +2382,901 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="B5" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="13" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="B22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E22" s="14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+    <row r="23" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="B24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="13" t="s">
+      <c r="B28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="B29" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="13" t="s">
+      <c r="B30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="B31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="13" t="s">
+      <c r="B32" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E32" s="14" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="13" t="s">
+      <c r="B33" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="13" t="s">
+      <c r="B34" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E34" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E35" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+    <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E36" s="14" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D38" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="13" t="s">
+      <c r="B39" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D39" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E39" s="14" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B40" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B41" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D41" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E41" s="14" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+    <row r="42" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C42" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+    <row r="43" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
+    <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="C44" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B41" s="13" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="B45" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="B42" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C42" s="13" t="s">
+      <c r="B46" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C43" s="13" t="s">
+      <c r="B47" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D47" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E47" s="14" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C44" s="13" t="s">
+      <c r="B48" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C45" s="13" t="s">
+      <c r="B49" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C49" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D49" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E49" s="14" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C46" s="13" t="s">
+      <c r="B50" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C50" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C47" s="13" t="s">
+      <c r="B51" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="B48" s="13" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="B52" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>332</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:E52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/deliverables/WMP/WMP__Solution_Design_Gap_Register__20260825.xlsx
+++ b/deliverables/WMP/WMP__Solution_Design_Gap_Register__20260825.xlsx
@@ -11,10 +11,11 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Gap Register" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Resolved Decisions" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Discovery Facts" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Gap Register'!$A$1:$K$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Resolved Decisions'!$A$1:$E$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Gap Register'!$A$1:$K$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Resolved Decisions'!$A$1:$E$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="370">
   <si>
     <t xml:space="preserve">WMP Solution Design — Inputs &amp; Decisions Gap Register</t>
   </si>
   <si>
-    <t xml:space="preserve">Rev 7 — 8/25/2026: call answers applied (decommission gate, post-Exchange ownership, operations scope). 13 call-ready rows remain.</t>
+    <t xml:space="preserve">Rev 8 — 8/25/2026: discovery-session facts applied — all 64 items resolved or transferred. Open actions/research now live on the Asana board ('Duplicate of Wisconsin Metal Parts', Discovery Action Items). Facts recorded on the Discovery Facts sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Wisconsin Metal Parts — Microsoft GCC High Migration (CMMC 2.0 Level 2)  |  Prepared by Essendis</t>
@@ -130,281 +131,6 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">G-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application and device mail flow has no design. The decommission gate requires printers, scanners, and ERP relay to be redirected to Exchange Online, but no relay method is defined — and the document already flags that the SPF record and the outbound disclaimer wording are unfinished.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open item in doc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a hard gate on WBS 9.1.5: on-premises Exchange cannot be removed until every relay client is redirected, and in GCC High the relay options (connector with certificate/IP, direct send, SMTP AUTH) each carry different prerequisites.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which devices and apps send email today — copiers/scanners, ERP, anything else?
-Do they support authenticated SMTP with TLS, or only basic/unauthenticated relay?
-Any high-volume senders (quotes, invoices, alerts)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exchange Online &gt; new "Application Mail Flow / SMTP Relay"; Email Authentication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essendis + WMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Room and resource mailboxes are undefined. The migration section lists user mailboxes, shared mailboxes, distribution lists, and groups — but not rooms, while the decommission gate and WBS 5.2.5 both assume room resource accounts exist and are recreated rather than migrated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Room mailboxes recreated rather than migrated lose their booking history and delegates, and any Teams Room or conference device tied to them needs its own licence and GCC High validation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How many room/equipment mailboxes, and their names?
-Any delegate-managed or special booking behaviours to preserve?
-Is room calendar history needed, or is a clean rebuild fine?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Known from WBS 5.2.5: room resource accounts are recreated in GCC High rather than migrated. The count is still recorded as TBD in WBS 1.1.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exchange Online; Migration Design &gt; Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How WMP collaborates with the outside world after go-live is undefined. External sharing is disabled in SharePoint and OneDrive, Teams guest access is off, external access is limited to "specific external domains" that are never listed, and CA policy 6 targets "Contractors" — a population that appears nowhere else. Encrypted email to external parties is also undefined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WMP is a subcontractor: it must exchange drawings, quotes, and CUI with primes and the DoD daily. Shipping a tenant with every external path closed and no approved alternative creates immediate shadow IT, and GCC High-to-commercial federation is materially restricted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which external orgs need Teams chat/meetings (primes, suppliers, Essendis, RPO) — for the allow list?
-Are there any guest users at all today? (If none, CA policy 6 is removed.)
-How is CUI exchanged with primes today, and what is the sanctioned path after go-live?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deploying purview message encryption. External orgs and guest inventory need established. External sharing approvals out of scope.
-WMP (8/25): Purview Message Encryption is being deployed; external-org and guest inventory still to be established; external-sharing approval workflow out of scope.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SharePoint &gt; External Sharing; Teams &gt; External and Guest Access; CA policy 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site and team provisioning governance is missing, and the SharePoint section twice says "see the appendix for a list of sites that will be migrated" — there is no such appendix (the document contains only Appendix A, password matrix, and Appendix B, terms of use).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBS 5.4.1 needs a source-to-destination site map before migration can be configured, and unrestricted team/site creation is how CUI sprawls into ungoverned locations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List the SharePoint sites and Teams to migrate, with owners.
-Who may create new Teams/sites after go-live — everyone, or IT only?
-Any naming standard to enforce?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Known bounds from the WBS: up to 5 SharePoint sites (1.1.6, 5.4.3), 15–20 shared mailboxes (1.1.2), light Teams adoption (1.1.5). The named inventory is still outstanding.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SharePoint &gt; Site Provisioning; new appendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificate and network-access dependencies are undefined. The mobile sections promise configuration profiles delivering "Wi-Fi, email, and VPN settings where required" with no authentication method or certificate source, and nothing at all covers Windows 802.1X once devices leave the domain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If corporate Wi-Fi uses 802.1X with machine certificates issued by AD auto-enrolment, every Entra-joined device loses network access at the moment of migration — and issuing certificates from Intune requires a SCEP/PKCS connector and a PKI that is not in scope anywhere.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How does corporate Wi-Fi authenticate at each site — PSK, or 802.1X with certificates?
-Is there an internal PKI (AD Certificate Services) today?
-Any VPN client in use, and does it need device certificates?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New section: Endpoint Configuration &gt; Certificates and Network Access; MDM configuration profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared and kiosk workstations on the shop floor are not addressed. The design assumes one identity per user and a compliant personal device; a fabrication floor typically runs shared terminals for time clocks, drawings, work instructions, and machine-tool control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared credentials break individual accountability under CMMC AC.L2-3.1.1 and IA.L2-3.5.1/3.5.2, and shared machines interact badly with a "require compliant device" CA policy and with per-user OneDrive/Known Folder Move.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Are there shared or kiosk PCs on the production floor — how many per site?
-Do floor workers have individual accounts, or shared logins?
-Do those terminals need M365 access, or only shop systems?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New section: Endpoint Configuration (Windows) &gt; Shared and Kiosk Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile fleet inputs are outstanding: the design records device counts by platform as TBD, leaves the MAM-only access path as an explicitly open item, and does not define which applications beyond Outlook and Teams are deployed or what the loss/wipe process is.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollout cannot be scheduled or licensed without counts, and "MAM-only if needed" left open means the enrolment restriction blocking personal devices may collide with a real business need at go-live.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How many corporate iPhones and Androids, by site?
-Does WMP have an Apple Business Manager account, and who owns it?
-Does anyone need MAM-only access, or is full enrolment universal?
-Any apps beyond Outlook/Teams to deploy to mobile?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essendis dictating app protection settings. Refresh/retire process out of scope.
-WMP (8/25): Essendis dictates the app-protection settings; device refresh/retire process out of scope.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDM (Intune) &gt; Pilot Validation and Rollout; Compliance and Conditional Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice endpoints are not inventoried. The design covers users and calling features but never mentions physical or analog endpoints — at a fabrication shop that typically means overhead paging, fax lines, elevator and door phones, alarm and monitoring lines, and loud-environment handsets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog and paging endpoints have no native path in Teams Phone; discovering them after porting means either a failed cutover or an unplanned ATA/paging gateway purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conference rooms: how many, what devices are in them today, and should any become Teams Rooms (GCC High-validated)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conference room devices are the only relevant question here
-WMP (8/25): conference room devices are the only relevant question here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teams Voice &gt; new "Voice Endpoints" subsection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WMP + CallTower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source data volumes and mailbox inventory are unquantified. The design names workload types but no counts or sizes; the WBS carries approximations (~150 users, 15–20 shared mailboxes, up to 5 SharePoint sites, rooms TBD) and no data on archives, public folders, or PSTs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume drives migration duration, bandwidth, batch sizing, and cost; unlisted artifact classes like public folders and PSTs are the ones that surface on cutover weekend with no plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approximate total mail data and largest mailboxes? (Or: when can we run the AvePoint discovery scan?)
-Any PST files, public folders, or a third-party mail archive?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Known WBS bounds: ~150 user mailboxes (5.2.3), up to 20 shared mailboxes (5.2.4), up to 5 SharePoint sites (5.4.3), room counts TBD (1.1.2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migration Design &gt; M365 Migration; new inventory appendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain transition mechanics are missing. The design covers DNS record repointing but not the constraint that wisconsinmetalparts.com must be removed from the commercial tenant before it can be added to GCC High (WBS 5.5.5/5.5.6), nor the transition domains, registrar access, TTL plan, or rollback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A vanity domain cannot exist in two tenants at once; the removal/re-add sequence creates a hard, irreversible window on cutover weekend that must be planned to the minute.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm the GCC High initial domain: wisconsinmetalparts.onmicrosoft.us, or something shorter? (Permanent — set at tenant creation.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We just need to confirm the expected domain works (versus something shorter)
-WMP (8/25): just confirm the expected domain works (versus something shorter). Runbook facts already set: &lt;1 hr release gap, TTL 30 min from 5 days out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entra ID &gt; Custom Domain; Migration Design &gt; Mail Flow Cutover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is no application integration inventory. The design's Constraints section mentions "third-party integrations referencing legacy URLs" but nothing enumerates the applications that authenticate to Entra ID, call Microsoft Graph, or integrate with mail and files — and many ISVs do not support GCC High endpoints at all.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An application that cannot be re-registered against GCC High becomes a go-live blocker discovered by users; WBS 9.1.4 also gates decommission on proving no application still authenticates to on-premises Exchange.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which business apps sign in with Microsoft 365 today (ERP, quoting, shipping, CAD/PDM)?
-Does anything read mailboxes/calendars or send mail as users (integrations)?
-Which service accounts must be excluded from MFA/CA?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New section: Assumptions &amp; Dependencies &gt; Application Integrations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The ForensIT profile conversion is described in six bullets with no execution detail: no per-device runbook, no handling of credential and encryption state, and no treatment of the application-level breakage that a domain-to-Entra identity change causes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BitLocker keys currently escrowed to on-premises AD do not follow the device to Entra; Windows Hello, cached credentials, saved application passwords, and mapped resources all reset at conversion. Any of these turns a 30-minute conversion into a rebuild.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conversion requires full decrypt + FIPS re-encrypt: confirm the per-device time window and wave sizing.
-On-site at each location or remote — and attended or scripted?
-Which applications break on the SID change and need re-activation (CAD/CAM, ERP)?
-Is the ForensIT licence purchased for the fleet size, and who runs the tool?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full decrypt required for FIPS cipher to apply.
-WMP (8/25): full decrypt required for the FIPS cipher to apply (decrypt, then re-encrypt under the FIPS policy).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migration Design &gt; Device Migration – ForensIT User Profile Wizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essendis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access to on-premises resources from Entra-joined devices is unaddressed. Once devices leave the domain, Kerberos-based access to file shares, print servers, and the ERP client stops working the way it does today — and the design never mentions it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is the most common post-migration outage in an Entra-join project: users lose mapped drives, printers, and application logins on the Monday after their device is converted, at three sites simultaneously.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which file shares and print servers do users touch daily?
-Drive mappings: rebuild via Intune scripts, or move the content to SharePoint?
-Printers after GPO retirement: print server, direct IP via Intune, or Universal Print?
-Does the ERP client require domain membership or Windows-integrated auth?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New section: Endpoint Configuration &gt; On-Premises Resource Access; Device Migration</t>
-  </si>
-  <si>
     <t xml:space="preserve">Item</t>
   </si>
   <si>
@@ -459,7 +185,8 @@
     <t xml:space="preserve">Migration schedule is undefined: cutover dates are listed as "TBD", the stated duration ("approximately 12 weeks</t>
   </si>
   <si>
-    <t xml:space="preserve">WMP (8/24): early-mid november - suggest available weekends.</t>
+    <t xml:space="preserve">WMP (8/24): early-mid november - suggest available weekends.
+Confirmed 8/25: cutover goal is mid-November. (The Asana board's 'cutover holds at 12/4-7' note is stale - update the board.)</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover targeted for early-to-mid November. Essendis proposes candidate weekends (avoiding Thanksgiving week), names the pilot batch in the migration plan, updates the stale 'first week of May' schedule text, and commits dates to CallTower and the communications plan.</t>
@@ -534,10 +261,10 @@
     <t xml:space="preserve">Device join model (design/WBS contradiction)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pure Entra join.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design/config actions: end state is Entra ID join (cloud-only). Simplify CA policy 3's grant to require-compliant-device only; remove the Seamless SSO section (a domain-joined-only feature); both join states coexist only during migration waves. Supersedes WBS 1.3.2's hybrid-join note. Cascade: closes G-08's sign-in-method question (PHS alone).</t>
+    <t xml:space="preserve">REVISED at discovery (8/25): the intended device strategy is Hybrid Azure AD Join with dual AD + Intune management; GPO remains in use (drive mappings, printers); RSA is retained for on-premises desktop MFA. This supersedes the earlier 'pure Entra join' answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design update: device join model is Entra hybrid join; CA policy 3 keeps 'compliant or hybrid-joined'; the earlier Seamless-SSO-removal and CA-simplification actions are ON HOLD; the WBS/board 'Modern Workspace - Entra join &amp; GPO retirement' phase conflicts with this and is addressed by the SOW-review action (Asana).</t>
   </si>
   <si>
     <t xml:space="preserve">G-10</t>
@@ -559,7 +286,8 @@
   </si>
   <si>
     <t xml:space="preserve">WMP (8/24): Admins should use passkey in authenticator or Yubikey
-WMP (8/24): shop-floor MFA = Microsoft Authenticator, with YubiKey as fallback.</t>
+WMP (8/24): shop-floor MFA = Microsoft Authenticator, with YubiKey as fallback.
+Discovery (8/25): RSA is retained for on-premises desktop MFA; the RSA Authenticator app deploys to mobile devices.</t>
   </si>
   <si>
     <t xml:space="preserve">MFA methods: admins use passkey in Authenticator or YubiKey; all other users Microsoft Authenticator with YubiKey fallback, including shop floor. Essendis plans pre-cutover registration (TAP or on-site sessions) in the communications plan, sizes the YubiKey purchase from the fallback-user list, and leaves SMS/voice methods disabled.</t>
@@ -640,6 +368,18 @@
     <t xml:space="preserve">Terms of Use delivered via Entra ID Terms of Use with a CA grant, applied to everyone, annual re-acceptance; WMP legal reviews the wording; bad cross-references corrected. SOC contact details are inserted into Appendix B when WMP establishes them.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application and device mail flow has no design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): senders are printers, the Epicor ERP, and the help-desk platform; TLS expected for supported devices; Pipedrive sends marketing/mailing-list mail via integration with the email platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essendis designs authenticated SMTP relay per sender class against Exchange Online GCC High (TLS where supported), and validates the Pipedrive integration after cutover.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-19</t>
   </si>
   <si>
@@ -652,6 +392,42 @@
     <t xml:space="preserve">Defender for Office 365: Strict preset policies; Safe Links everywhere and Safe Attachments for SPO/OneDrive/Teams (flagged files quarantined); quarantine release is admin-only. Notification recipients default to the admin team until WMP names a monitored mailbox.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room and resource mailboxes are undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): five conference rooms today with more planned at the new facility; no special booking regimes surfaced; no Teams Rooms planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room/equipment mailboxes are created fresh in GCC High at configuration (per WBS 5.2.5); calendar history rebuilds clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How WMP collaborates with the outside world after go-live is undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): guest accounts are used mainly for SharePoint file sharing, not Teams; Kiteworks currently handles external CUI exchange and the objective is to replace it with SharePoint external sharing; free/busy sharing with two sister organisations should be preserved if possible; Purview Message Encryption is being deployed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essendis designs the SharePoint external-sharing model for CUI (Kiteworks replacement — Asana research item); the external allow list is built from the sister orgs and partners at implementation; cross-tenant free/busy feasibility is an Asana research item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site and team provisioning governance is missing, and the SharePoint section twice says "see the appendix for a list of sites that will be migrated" — there is no such appendix (the document contains only Appendix A, password matrix, and Appendix B, terms of use)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): five SharePoint sites confirmed for migration; departments are evaluating additional Teams/SharePoint assets; some assets belong to M365 Groups, others were created independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migration list = the five confirmed sites plus departmental additions (Asana action tracks the evaluation); provisioning governance set at configuration.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-23</t>
   </si>
   <si>
@@ -736,6 +512,30 @@
     <t xml:space="preserve">GPO export, Intune equivalence mapping, and the exceptions list proceed as committed in WBS 4.2 during the Intune workstream; exceptions go to WMP decision/POA&amp;M; GPO unlink sign-off per WBS 7.3.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate and network-access dependencies are undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): an on-premises PKI is in place (device certificates and NAC); FortiGate SSL VPN with FortiClient EMS (~34 remote users, one fully remote), M365 auth integration desired post-migration; two sites have guest-only Wi-Fi; the new third site gets corporate Wi-Fi via RADIUS (NPS or ClearPass), operational mid-November; site-to-site VPNs link the sites and the Azure Government ERP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essendis designs FortiGate/Entra authentication integration; site-3 Wi-Fi design aligns to the PKI keep-or-replace decision (Asana research item).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared and kiosk workstations on the shop floor are not addressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): user population is heavily shop-floor with ~50 information workers; shared shop-floor PCs exist but WMP is moving to individual sign-ins; ~40 shop-floor devices need M365 access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design assumes individual credentials on the floor; ~40 shop-floor devices included in Intune scope and the F3 licence tier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-32</t>
   </si>
   <si>
@@ -748,6 +548,18 @@
     <t xml:space="preserve">No macOS devices exist: Essendis removes macOS from the CA policy 3 platform list (design edit).</t>
   </si>
   <si>
+    <t xml:space="preserve">G-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile fleet inputs are outstanding: the design records device counts by platform as TBD, leaves the MAM-only access path as an explicitly open item, and does not define which applications beyond Outlook and Teams are deployed or what the loss/wipe process is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): no corporate mobile devices today; planned deployment under 40 devices across iOS and Android; no BYOD; apps: Outlook, Teams, OneDrive, RSA Authenticator, Keeper; Apple Business Manager and Google Android management are not yet configured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDM section updated to a greenfield rollout with the five named apps; ABM/Android-platform setup timing and the platform-mix recommendation are Asana research items.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-34</t>
   </si>
   <si>
@@ -772,6 +584,18 @@
     <t xml:space="preserve">Number/DID inventory, carrier facts, and the porting LOA are produced during CallTower pre-integration planning as the design commits; licensing already fixes the phone population (55 BP-tier + 15 G5; no frontline phones).</t>
   </si>
   <si>
+    <t xml:space="preserve">G-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice endpoints are not inventoried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): five conference rooms (more at the new facility) using dedicated Windows devices or user laptops with existing AV; no Teams Rooms deployment planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design records no Teams Rooms in scope; rooms continue the current AV pattern.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-37</t>
   </si>
   <si>
@@ -796,6 +620,18 @@
     <t xml:space="preserve">No further action: Fly supports Commercial-to-GCC High; source Global Admin available for the whole window; AvePoint SaaS runs in Azure East US; app-consent/throttling tracking waived by WMP.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source data volumes and mailbox inventory are unquantified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): ~20 PST archives (~50 GB combined) to merge back into active mailboxes; no third-party mail archive beyond backups; WMP can rapidly support discovery once instructions arrive, and custom scripts require review before execution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PST ingestion into mailboxes is added to the migration plan; mailbox/site sizing comes from the AvePoint discovery scan once scripts are provided and approved (Asana action).</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-40</t>
   </si>
   <si>
@@ -808,6 +644,18 @@
     <t xml:space="preserve">Design input: single cutover event — coexistence window minimal, no cross-tenant free/busy or Teams federation needed.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain transition mechanics are missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): production email domain is wisconsinmetalparts.com; the default *.onmicrosoft.us initial domain is acceptable at setup. The 'wmparts.onmicrosoft.us' value on the Asana board is wrong and must not be kept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design records wisconsinmetalparts.com as the primary SMTP/vanity domain and the default onmicrosoft.us as the initial domain; correct the erroneous tenant strings in the design ('.microsoftonline.us') and on the Asana board.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-42</t>
   </si>
   <si>
@@ -820,6 +668,18 @@
     <t xml:space="preserve">Design input: chat/channel migration confirmed supported; Planner, Forms, Viva, Power Automate, Power Apps, Power BI are out of migration scope.</t>
   </si>
   <si>
+    <t xml:space="preserve">G-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no application integration inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): no applications authenticate through M365 today (long-term goal: move several to Entra ID); NinjaOne, Keeper, and Fortra access mailboxes/calendars; service accounts are on-premises in a dedicated OU; multiple LOB and manufacturing systems authenticate against AD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-consent NinjaOne/Keeper/Fortra integrations against GCC High at migration; the OU and service-account inventory is an Asana action; Entra ID app-auth adoption is a post-migration roadmap item.</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-44</t>
   </si>
   <si>
@@ -856,13 +716,38 @@
     <t xml:space="preserve">Windows device inventory by site/type is collected by WMP during pre-migration device preparation (WBS 7.1.1); Windows 11/TPM exceptions are handled wave-by-wave; servers remain out of scope (G-28).</t>
   </si>
   <si>
+    <t xml:space="preserve">G-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ForensIT profile conversion is described in six bullets with no execution detail: no per-device runbook, no handling of credential and encryption state, and no treatment of the application-level breakage that a domain-to-Entra identity change causes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): all devices can be brought into the office for migration/encryption work; NinjaOne is the RMM and can push commands and packages; application deployment continues through NinjaOne rather than Intune; conversion requires full decrypt before FIPS re-encryption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversion runbook: in-office waves executed/scripted via NinjaOne; application redeployment via NinjaOne (Intune app deployment descoped accordingly); decrypt/re-encrypt time boxed per wave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access to on-premises resources from Entra-joined devices is unaddressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery (8/25): two print servers; three file servers reducing to two (~7 TB, UNC paths, no DFS); drive mappings deployed via GPO; printer management remains GPO-based (Kyocera MyPrint under evaluation); hybrid Azure AD Join is the intended device strategy, so AD Kerberos access continues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With hybrid join, on-premises file/print access continues over AD Kerberos and drive maps/printing stay GPO-delivered; the WBS/board 'GPO retirement' phase is superseded pending the SOW review (Asana action).</t>
+  </si>
+  <si>
     <t xml:space="preserve">G-49</t>
   </si>
   <si>
     <t xml:space="preserve">The pre-decommission gate lists what must be true but not how it is proven</t>
   </si>
   <si>
-    <t xml:space="preserve">WMP (8/25, via chat): 7-day monitored hold; Kyle Mandersfield signs the decommission authorization.</t>
+    <t xml:space="preserve">WMP (8/25, via chat): 7-day monitored hold; Kyle Mandersfield signs the decommission authorization.
+Discovery (8/25): decommission sequencing is in flux - leaning post-cutover (as the design documents). Material reframing: on-prem Exchange 2016 is a MANAGEMENT platform only - all mailboxes and mail flow moved to M365 commercial previously - so decommission is hybrid-config/management-server removal, not a mail migration.</t>
   </si>
   <si>
     <t xml:space="preserve">Design update: the pre-removal monitored hold is 7 days and the decommission authorization is signed by Kyle Mandersfield (WMP). Essendis defines the residual-connection evidence check within that window.</t>
@@ -898,7 +783,8 @@
     <t xml:space="preserve">There is no monitoring or alerting design</t>
   </si>
   <si>
-    <t xml:space="preserve">WMP (8/25, via chat): Operations and support are out of scope.</t>
+    <t xml:space="preserve">WMP (8/25, via chat): Operations and support are out of scope.
+Discovery (8/25): Arctic Wolf is the SIEM platform and will need visibility into the GCC High environment.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope decision: monitoring, alerting, and log-review design are out of engagement scope — WMP decides (an Azure subscription exists if Log Analytics is wanted). Essendis's remaining action is the G-03 cleanup: reword the design's break-glass 'Log Analytics in Azure' reference to reflect WMP-owned alerting.</t>
@@ -910,7 +796,8 @@
     <t xml:space="preserve">Backup and recoverability for M365 data is not addressed</t>
   </si>
   <si>
-    <t xml:space="preserve">Backups out of scope.</t>
+    <t xml:space="preserve">Backups out of scope.
+Discovery (8/25): ArcServe does not support GCC High; WMP is already evaluating replacement backup solutions (Asana action).</t>
   </si>
   <si>
     <t xml:space="preserve">Scope decision: Microsoft 365 backup out of scope — native retention, versioning, and recycle bins accepted.</t>
@@ -1052,6 +939,219 @@
   </si>
   <si>
     <t xml:space="preserve">Scope decision: no diagrams in scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fact (discovery session, recorded 8/25/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First discovery session with the client; prior work was a kickoff meeting only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: a GCC High environment that upgrades and closely mirrors the current environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current licensing: Microsoft 365 Commercial with Business Standard and Business Basic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSA addresses authentication requirements today and is retained for desktop MFA on-premises.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment is predominantly on-premises; cloud workloads are limited to M365 email and an Epicor ERP hosted in Azure Government.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All file storage is on-premises.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FortiGate SSL VPN in use; M365 authentication integration desired after migration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-premises PKI in place, used for device certificates and network access control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSPR in M365 is of interest; other tools (Netwrix, ManageEngine) also being evaluated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User population heavily shop-floor; approximately 50 information workers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exchange 2016 remains on-premises as a management platform only; mailboxes and mail flow migrated to M365 previously.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identities continue synchronizing from on-prem AD; the on-prem Exchange server should be eliminated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devices sending email: printers, ERP systems, help-desk platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTP relay requirements exist; TLS expected for supported devices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipedrive sends marketing/mailing-list communications via integration with the email platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar sharing exists with two sister organizations; free/busy sharing should be maintained if possible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External guest accounts are used primarily for SharePoint file sharing, not Teams collaboration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiteworks is used today for external CUI file exchange.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objective: replace Kiteworks with SharePoint for external file sharing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five SharePoint sites confirmed for migration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Teams/SharePoint sites are being evaluated by departments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some Teams/SharePoint assets belong to M365 Groups; others were created independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three locations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two locations currently provide guest wireless only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New third location under construction receives corporate Wi-Fi via RADIUS (NPS or ClearPass).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-site occupancy began August 1; operational readiness targeted mid-November.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site-to-site VPN connectivity exists between locations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each location connects to the Azure Government ERP environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FortiClient EMS manages SSL VPN for remote workers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~34 users use remote access; one employee is fully remote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared shop-floor PCs exist; moving away from shared credentials to individual sign-ins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~40 shop-floor devices will require M365 access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intended Windows management strategy: hybrid management with both AD and Intune.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No corporate mobile devices today; deployment planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Future mobile deployment expected under 40 devices, iOS and Android.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BYOD will not be supported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile apps: Outlook, Teams, OneDrive, RSA Authenticator, Keeper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Business Manager and Google mobile management platforms not yet configured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five conference rooms today; additional rooms planned at the new facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conference rooms use dedicated Windows devices or user laptops with existing AV equipment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Teams Rooms deployment currently planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client can rapidly support discovery activities after receiving instructions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom discovery scripts require review before execution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~20 PST archives (~50 GB combined) should be merged back into active mailboxes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No third-party email archive platform beyond backup solutions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArcServe backups do not support GCC High; replacement solutions being evaluated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Government ERP is managed by Epicor; the client has no direct Azure administrative access.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organization is tenant owner of record; Epicor is authorized reseller and manager.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred production email domain for GCC High: wisconsinmetalparts.com.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client is comfortable with a default onmicrosoft.us domain during setup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No applications authenticate through M365 today; long-term goal is Entra ID authentication for several apps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-party applications accessing M365 mailboxes/calendars: NinjaOne, Keeper, Fortra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service accounts are primarily on-premises in a dedicated OU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All devices can be physically brought into the office for migration and encryption activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NinjaOne is used for device management and software deployment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application deployment continues through NinjaOne rather than Intune.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two print servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three file servers, reducing to two.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File services available across all sites via VPN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFS Namespaces not in use; standard UNC paths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total file-share storage ~7 TB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive mappings deployed through Group Policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printer management remains GPO-based; Kyocera MyPrint under evaluation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hybrid Azure AD Join remains the intended device strategy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arctic Wolf is the current SIEM and needs visibility into GCC High.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple line-of-business applications authenticate directly against on-prem AD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturing systems and file services depend on Active Directory accounts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cutover goal: mid-November (per M. Schraepfer, 8/25).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decommission sequencing in flux - leaning post-cutover.</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1273,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1184,18 +1284,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4E4"/>
-        <bgColor rgb="FFFFF3DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3DC"/>
-        <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1248,7 +1336,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1305,19 +1393,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1330,18 +1410,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F4E79"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1357,15 +1430,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4E4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3DC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1391,7 +1455,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF3DC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1412,7 +1476,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4E4"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1714,14 +1778,14 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B18)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!J:J,"High")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1730,14 +1794,14 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B19)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!J:J,"Medium")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1746,14 +1810,14 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B20)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">COUNTA('Gap Register'!A:A)-1</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1762,14 +1826,14 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">COUNTA('Resolved Decisions'!A:A)-1</f>
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1778,7 +1842,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B22)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1787,7 +1851,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">COUNTIF('Gap Register'!B:B,B23)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1881,491 +1945,215 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
       <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>67</v>
-      </c>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>72</v>
-      </c>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
       <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>102</v>
-      </c>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="14"/>
-      <c r="H12" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>114</v>
-      </c>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
       <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>42</v>
-      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2382,7 +2170,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2399,884 +2187,1105 @@
         <v>26</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="13" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="B21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+      <c r="D21" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="E21" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="D25" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="14" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="D26" s="15" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="E26" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="B27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D27" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E27" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D29" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="E29" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="14" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="B30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="E30" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="14" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="B31" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="E31" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E11" s="14" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="B32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E32" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="E12" s="14" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="B33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E33" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="14" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="B34" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="E34" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="E14" s="14" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="B35" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="D35" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D15" s="14" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="B36" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="D36" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="14" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="B37" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="D37" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="E37" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="14" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="B38" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="D38" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="E38" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="14" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="B39" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="D39" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="E39" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D19" s="14" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="B40" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="D40" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="E40" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="D20" s="14" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="B41" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="D41" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="E41" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="14" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="B42" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="D42" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="E42" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="D22" s="14" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="B43" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="D43" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="E43" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="14" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="B44" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="D44" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="E44" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="14" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="B45" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="D45" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="14" t="s">
+      <c r="E45" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="14" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="B46" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="D46" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="14" t="s">
+      <c r="E46" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="D26" s="14" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="B47" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="D47" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="14" t="s">
+      <c r="E47" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="D27" s="14" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="B48" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="D48" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="14" t="s">
+      <c r="E48" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="14" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="B49" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="D49" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="E49" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="D29" s="14" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="B50" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+      <c r="D50" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="E50" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="14" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="B51" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
+      <c r="D51" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="E51" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="D31" s="14" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="B52" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
+      <c r="D52" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="E52" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="D32" s="14" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="B53" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
+      <c r="D53" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="14" t="s">
+      <c r="E53" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="D33" s="14" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="B54" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
+      <c r="D54" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="14" t="s">
+      <c r="E54" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="D34" s="14" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="B55" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
+      <c r="D55" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="14" t="s">
+      <c r="E55" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="14" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="B56" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
+      <c r="D56" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="E56" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="D36" s="14" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="B57" s="15" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
+      <c r="C57" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="D57" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="E57" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="E37" s="14" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
+      <c r="B58" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="D58" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="E58" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="E38" s="14" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
+      <c r="B59" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="D59" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="E59" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="E39" s="14" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
+      <c r="B60" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C60" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="D60" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="E60" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="E40" s="14" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14" t="s">
+      <c r="B61" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="D61" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="E61" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E41" s="14" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
+      <c r="B62" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="14" t="s">
+      <c r="D62" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="E62" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="E42" s="14" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="s">
+      <c r="B63" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="D63" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="E63" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="E43" s="14" t="s">
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="s">
+      <c r="B64" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="C64" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="D64" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="E64" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E44" s="14" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="s">
+      <c r="B65" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="D65" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="E65" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>328</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E52"/>
+  <autoFilter ref="A1:E65"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3286,4 +3295,587 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B70"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>